--- a/auto OMS Python/engines/shopee/media_chihuy2309.xlsx
+++ b/auto OMS Python/engines/shopee/media_chihuy2309.xlsx
@@ -3423,6 +3423,51 @@
     <t>1 Đầu Vạn Năng K50</t>
   </si>
   <si>
+    <t>13040839585</t>
+  </si>
+  <si>
+    <t>Khay Lọc Rác ABS Kèm Miếng Dán Nano K98 – Giải Pháp Chống Tắc Nghẽn Cực Kỳ Hiệu Quả</t>
+  </si>
+  <si>
+    <t>101232 - Home &amp; Living/Kitchenware/Strainers</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/a05809c4cf63e8b2d9432d79644a9292</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/c9f085b33ae7419bd44d5cd042482483</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/2a6d6755dc5710d8229c50cb33a13070</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/4175369fc5c2c6972818884692789d57</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/9174166802fde6e1745416bff9ed9e47</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/65d37f09517639d6cce7c6717ebaeebc</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/a6e3691efc8ac2225f5a1e422c358937</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/813f26645d5c8f904c1e0b28bf00fa41</t>
+  </si>
+  <si>
+    <t>Khung Xám + 50 TÚI</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8j9d2xwig7e</t>
+  </si>
+  <si>
+    <t>Khung Xanh + 50 TÚI</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8jbevxw8m17</t>
+  </si>
+  <si>
     <t>11277881543</t>
   </si>
   <si>
@@ -3484,51 +3529,6 @@
   </si>
   <si>
     <t>https://cf.shopee.vn/file/e91806db22a6e3f492bb85023c03c214</t>
-  </si>
-  <si>
-    <t>13040839585</t>
-  </si>
-  <si>
-    <t>Khay Lọc Rác ABS Kèm Miếng Dán Nano K98 – Giải Pháp Chống Tắc Nghẽn Cực Kỳ Hiệu Quả</t>
-  </si>
-  <si>
-    <t>101232 - Home &amp; Living/Kitchenware/Strainers</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/a05809c4cf63e8b2d9432d79644a9292</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/c9f085b33ae7419bd44d5cd042482483</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/2a6d6755dc5710d8229c50cb33a13070</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/4175369fc5c2c6972818884692789d57</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/9174166802fde6e1745416bff9ed9e47</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/65d37f09517639d6cce7c6717ebaeebc</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/a6e3691efc8ac2225f5a1e422c358937</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/813f26645d5c8f904c1e0b28bf00fa41</t>
-  </si>
-  <si>
-    <t>Khung Xám + 50 TÚI</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8j9d2xwig7e</t>
-  </si>
-  <si>
-    <t>Khung Xanh + 50 TÚI</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8jbevxw8m17</t>
   </si>
   <si>
     <t>3124379936</t>
@@ -10840,26 +10840,32 @@
         <v>1136</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>352</v>
+        <v>1137</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>1141</v>
-      </c>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
+        <v>1142</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>1145</v>
+      </c>
       <c r="M87" s="3"/>
       <c r="N87" s="10"/>
       <c r="O87" s="10"/>
@@ -10867,13 +10873,17 @@
         <v>145</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>1138</v>
-      </c>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
+        <v>1147</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>1149</v>
+      </c>
       <c r="U87" s="10"/>
       <c r="V87" s="10"/>
       <c r="W87" s="10"/>
@@ -10894,52 +10904,44 @@
     </row>
     <row customHeight="true" ht="15" r="88">
       <c r="A88" s="1" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>877</v>
+        <v>352</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>1153</v>
-      </c>
+        <v>1156</v>
+      </c>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
       <c r="N88" s="10"/>
       <c r="O88" s="10"/>
       <c r="P88" s="2" t="s">
         <v>145</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="S88" s="10"/>
       <c r="T88" s="10"/>
@@ -10963,57 +10965,55 @@
     </row>
     <row customHeight="true" ht="15" r="89">
       <c r="A89" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1158</v>
+        <v>877</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>1166</v>
-      </c>
-      <c r="M89" s="3"/>
+        <v>1167</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>1168</v>
+      </c>
       <c r="N89" s="10"/>
       <c r="O89" s="10"/>
       <c r="P89" s="2" t="s">
         <v>145</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>1168</v>
-      </c>
-      <c r="S89" s="2" t="s">
-        <v>1169</v>
-      </c>
-      <c r="T89" s="3" t="s">
         <v>1170</v>
       </c>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
       <c r="U89" s="10"/>
       <c r="V89" s="10"/>
       <c r="W89" s="10"/>
